--- a/Sales Data.xlsx
+++ b/Sales Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Excel\Excel_Project_Work\Project 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58ADE6B-66DE-44E4-AAEF-9B5781CDF40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BF0B54-A3C5-497B-A38A-83B8851256AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A03000F-CE6F-434D-94EB-643CC0F60A3A}"/>
   </bookViews>
@@ -20,30 +20,35 @@
     <sheet name="Regression &amp; Statistics" sheetId="3" r:id="rId5"/>
     <sheet name="Monthy Sales" sheetId="6" r:id="rId6"/>
     <sheet name="Total Sales" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet3" sheetId="14" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data!$A$1:$A$201</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Top 10'!$A$2:$G$32</definedName>
+    <definedName name="NativeTimeline_Order_Date">#N/A</definedName>
     <definedName name="Slicer_Months__Order_Date">#N/A</definedName>
     <definedName name="Slicer_Product_Category">#N/A</definedName>
     <definedName name="Slicer_Region">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId9"/>
-    <pivotCache cacheId="4" r:id="rId10"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
+        <x14:slicerCache r:id="rId10"/>
         <x14:slicerCache r:id="rId11"/>
         <x14:slicerCache r:id="rId12"/>
-        <x14:slicerCache r:id="rId13"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
+      <x15:timelineCacheRefs>
+        <x15:timelineCacheRef r:id="rId13"/>
+      </x15:timelineCacheRefs>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -549,25 +554,108 @@
     <t>Key Insights — Sales Dashboard</t>
   </si>
   <si>
-    <t>4. September 2024 was peak month (₹20,534); April 2025 dropped sharply (₹3,212) — needs verification (may be incomplete data)</t>
+    <t>Q6. TimeStamp</t>
   </si>
   <si>
-    <t>3. Books is the top category (₹47,002); Office Supplies is weakest (₹28,631)</t>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Total Sales: ₹1,95,218 | Total Profit: ₹68,287 (35% margin) across 200 orders, 13 months</t>
+    </r>
   </si>
   <si>
-    <t>2.West region leads at ₹44,084; East trails at ₹32,442 — a 26% performance gap</t>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>West region leads at ₹44,084; East trails at ₹32,442 — a 26% performance gap</t>
+    </r>
   </si>
   <si>
-    <t>1. Total Sales: ₹1,95,218 | Total Profit: ₹68,287 (35% margin) across 200 orders, 13 months</t>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Books is the top category (₹47,002); Office Supplies is weakest (₹28,631)</t>
+    </r>
   </si>
   <si>
-    <t>5. 10 of 27 customers (37%) drive most of the revenue — top customer: James Wilson (₹20,775)</t>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>September 2024 was peak month (₹20,534); April 2025 dropped sharply (₹3,212) — needs verification (may be incomplete data)</t>
+    </r>
   </si>
   <si>
-    <t>6. Every ₹1 in sales adds ₹0.35 in profit, with sales explaining ~60% of profit variation (R² = 0.60)</t>
+    <r>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10 of 27 customers (37%) drive most of the revenue — top customer: James Wilson (₹20,775</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
-    <t>Q6. TimeStamp</t>
+    <r>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Every ₹1 in sales adds ₹0.35 in profit, with sales explaining ~60% of profit variation (R² = 0.60)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -580,7 +668,7 @@
     <numFmt numFmtId="166" formatCode="General\ \%"/>
     <numFmt numFmtId="167" formatCode="[$₹-4009]\ #,##0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,6 +777,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -734,7 +829,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1083,14 +1178,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="double">
         <color theme="0"/>
-      </left>
-      <right/>
+      </right>
       <top style="double">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="double">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1099,35 +1196,7 @@
       <top style="double">
         <color theme="0"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color theme="0"/>
       </bottom>
       <diagonal/>
@@ -1370,23 +1439,44 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1433,33 +1523,12 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1533,378 +1602,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2081,10 +1778,6 @@
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2381,6 +2074,378 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" indent="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="[$₹-4009]\ #,##0.00"/>
       <fill>
         <patternFill patternType="none">
@@ -2533,6 +2598,10 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3076,28 +3145,20 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:glow rad="101600">
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                      <a:alpha val="60000"/>
-                    </a:schemeClr>
-                  </a:glow>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="2000"/>
               <a:t>Sales by Region &amp; catagory</a:t>
             </a:r>
           </a:p>
@@ -3124,21 +3185,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:glow rad="101600">
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                    <a:alpha val="60000"/>
-                  </a:schemeClr>
-                </a:glow>
-              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -3341,7 +3394,49 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3361,19 +3456,11 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:effectLst>
-                    <a:glow rad="101600">
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                        <a:alpha val="60000"/>
-                      </a:schemeClr>
-                    </a:glow>
-                  </a:effectLst>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
@@ -3434,7 +3521,49 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3454,19 +3583,11 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:effectLst>
-                    <a:glow rad="101600">
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                        <a:alpha val="60000"/>
-                      </a:schemeClr>
-                    </a:glow>
-                  </a:effectLst>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
@@ -3527,7 +3648,49 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent3">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3547,19 +3710,11 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:effectLst>
-                    <a:glow rad="101600">
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                        <a:alpha val="60000"/>
-                      </a:schemeClr>
-                    </a:glow>
-                  </a:effectLst>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
@@ -3620,7 +3775,49 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3640,19 +3837,11 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:effectLst>
-                    <a:glow rad="101600">
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                        <a:alpha val="60000"/>
-                      </a:schemeClr>
-                    </a:glow>
-                  </a:effectLst>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
@@ -3713,7 +3902,49 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent5">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent5">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3733,19 +3964,11 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:effectLst>
-                    <a:glow rad="101600">
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                        <a:alpha val="60000"/>
-                      </a:schemeClr>
-                    </a:glow>
-                  </a:effectLst>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
@@ -3767,86 +3990,8 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="15"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:effectLst>
-                    <a:glow rad="101600">
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                        <a:alpha val="60000"/>
-                      </a:schemeClr>
-                    </a:glow>
-                  </a:effectLst>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -4433,9 +4578,9 @@
           <a:noFill/>
           <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -4447,21 +4592,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:glow rad="101600">
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                      <a:alpha val="60000"/>
-                    </a:schemeClr>
-                  </a:glow>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
@@ -4488,9 +4625,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -4507,15 +4644,7 @@
           <a:ln>
             <a:noFill/>
           </a:ln>
-          <a:effectLst>
-            <a:glow rad="101600">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="85000"/>
-                <a:lumOff val="15000"/>
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:glow>
-          </a:effectLst>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
@@ -4524,19 +4653,11 @@
             <a:pPr>
               <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:glow rad="101600">
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                      <a:alpha val="60000"/>
-                    </a:schemeClr>
-                  </a:glow>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
@@ -4572,21 +4693,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="85000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:glow rad="101600">
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                    <a:alpha val="60000"/>
-                  </a:schemeClr>
-                </a:glow>
-              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -4608,57 +4721,26 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
+      <a:round/>
     </a:ln>
-    <a:effectLst>
-      <a:glow rad="101600">
-        <a:schemeClr val="tx1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-          <a:alpha val="60000"/>
-        </a:schemeClr>
-      </a:glow>
-    </a:effectLst>
+    <a:effectLst/>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr>
-          <a:effectLst>
-            <a:glow rad="101600">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="85000"/>
-                <a:lumOff val="15000"/>
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:glow>
-          </a:effectLst>
-        </a:defRPr>
+        <a:defRPr/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -4712,28 +4794,20 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:glow rad="101600">
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                      <a:alpha val="60000"/>
-                    </a:schemeClr>
-                  </a:glow>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="2400"/>
               <a:t>Quantity Sold Per Region</a:t>
             </a:r>
           </a:p>
@@ -4760,21 +4834,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:glow rad="101600">
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                    <a:alpha val="60000"/>
-                  </a:schemeClr>
-                </a:glow>
-              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -4834,50 +4900,28 @@
       <c:pivotFmt>
         <c:idx val="7"/>
         <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
             </a:outerShdw>
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront"/>
             <a:lightRig rig="threePt" dir="t"/>
           </a:scene3d>
-          <a:sp3d/>
+          <a:sp3d prstMaterial="matte"/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4889,25 +4933,16 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
                 <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="lt1"/>
                   </a:solidFill>
-                  <a:effectLst>
-                    <a:glow rad="101600">
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                        <a:alpha val="60000"/>
-                      </a:schemeClr>
-                    </a:glow>
-                  </a:effectLst>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
@@ -4916,7 +4951,7 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="1"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -4932,239 +4967,125 @@
       <c:pivotFmt>
         <c:idx val="8"/>
         <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
             </a:outerShdw>
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront"/>
             <a:lightRig rig="threePt" dir="t"/>
           </a:scene3d>
-          <a:sp3d/>
+          <a:sp3d prstMaterial="matte"/>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="9"/>
         <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
             </a:outerShdw>
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront"/>
             <a:lightRig rig="threePt" dir="t"/>
           </a:scene3d>
-          <a:sp3d/>
+          <a:sp3d prstMaterial="matte"/>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="10"/>
         <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
             </a:outerShdw>
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront"/>
             <a:lightRig rig="threePt" dir="t"/>
           </a:scene3d>
-          <a:sp3d/>
+          <a:sp3d prstMaterial="matte"/>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="11"/>
         <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
             </a:outerShdw>
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront"/>
             <a:lightRig rig="threePt" dir="t"/>
           </a:scene3d>
-          <a:sp3d/>
+          <a:sp3d prstMaterial="matte"/>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="12"/>
         <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
             </a:outerShdw>
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront"/>
             <a:lightRig rig="threePt" dir="t"/>
           </a:scene3d>
-          <a:sp3d/>
+          <a:sp3d prstMaterial="matte"/>
         </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:view3D>
-      <c:rotX val="30"/>
+      <c:rotX val="50"/>
       <c:rotY val="0"/>
       <c:depthPercent val="100"/>
       <c:rAngAx val="0"/>
+      <c:perspective val="60"/>
     </c:view3D>
     <c:floor>
       <c:thickness val="0"/>
@@ -5217,58 +5138,28 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t"/>
-            </a:scene3d>
-            <a:sp3d/>
-          </c:spPr>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
                 </a:outerShdw>
               </a:effectLst>
               <a:scene3d>
                 <a:camera prst="orthographicFront"/>
                 <a:lightRig rig="threePt" dir="t"/>
               </a:scene3d>
-              <a:sp3d/>
+              <a:sp3d prstMaterial="matte"/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5280,47 +5171,24 @@
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent2">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent2">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent2">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
                 </a:outerShdw>
               </a:effectLst>
               <a:scene3d>
                 <a:camera prst="orthographicFront"/>
                 <a:lightRig rig="threePt" dir="t"/>
               </a:scene3d>
-              <a:sp3d/>
+              <a:sp3d prstMaterial="matte"/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5332,47 +5200,24 @@
             <c:idx val="2"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent3">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent3">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent3">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
                 </a:outerShdw>
               </a:effectLst>
               <a:scene3d>
                 <a:camera prst="orthographicFront"/>
                 <a:lightRig rig="threePt" dir="t"/>
               </a:scene3d>
-              <a:sp3d/>
+              <a:sp3d prstMaterial="matte"/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5384,47 +5229,24 @@
             <c:idx val="3"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent4">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent4">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent4">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
                 </a:outerShdw>
               </a:effectLst>
               <a:scene3d>
                 <a:camera prst="orthographicFront"/>
                 <a:lightRig rig="threePt" dir="t"/>
               </a:scene3d>
-              <a:sp3d/>
+              <a:sp3d prstMaterial="matte"/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5436,47 +5258,24 @@
             <c:idx val="4"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent5">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent5">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent5">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
                 </a:outerShdw>
               </a:effectLst>
               <a:scene3d>
                 <a:camera prst="orthographicFront"/>
                 <a:lightRig rig="threePt" dir="t"/>
               </a:scene3d>
-              <a:sp3d/>
+              <a:sp3d prstMaterial="matte"/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5493,25 +5292,16 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="lt1"/>
                     </a:solidFill>
-                    <a:effectLst>
-                      <a:glow rad="101600">
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="85000"/>
-                          <a:lumOff val="15000"/>
-                          <a:alpha val="60000"/>
-                        </a:schemeClr>
-                      </a:glow>
-                    </a:effectLst>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
@@ -5520,7 +5310,7 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
+            <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="1"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -5531,13 +5321,14 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="9525">
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                   <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="95000"/>
-                      <a:alpha val="54000"/>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
                     </a:schemeClr>
                   </a:solidFill>
+                  <a:round/>
                 </a:ln>
                 <a:effectLst/>
               </c:spPr>
@@ -5600,7 +5391,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="bestFit"/>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -5622,7 +5413,11 @@
       <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="78000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -5633,21 +5428,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:glow rad="101600">
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                    <a:alpha val="60000"/>
-                  </a:schemeClr>
-                </a:glow>
-              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -5669,57 +5456,33 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
+    <a:pattFill prst="dkDnDiag">
+      <a:fgClr>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="lt1"/>
+      </a:bgClr>
+    </a:pattFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
+      <a:round/>
     </a:ln>
-    <a:effectLst>
-      <a:glow rad="101600">
-        <a:schemeClr val="tx1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-          <a:alpha val="60000"/>
-        </a:schemeClr>
-      </a:glow>
-    </a:effectLst>
+    <a:effectLst/>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr>
-          <a:effectLst>
-            <a:glow rad="101600">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="85000"/>
-                <a:lumOff val="15000"/>
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:glow>
-          </a:effectLst>
-        </a:defRPr>
+        <a:defRPr/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -5769,26 +5532,20 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="2000"/>
               <a:t>Top 10 Sales</a:t>
             </a:r>
           </a:p>
@@ -5807,19 +5564,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -5962,6 +5713,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -5989,9 +5741,9 @@
           <a:noFill/>
           <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -6003,10 +5755,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -6035,9 +5788,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -6061,10 +5814,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -6099,28 +5853,17 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -6149,10 +5892,10 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="106"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="6"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
@@ -6167,34 +5910,27 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:glow rad="101600">
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                      <a:alpha val="60000"/>
-                    </a:schemeClr>
-                  </a:glow>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="2000" u="none"/>
               <a:t>Sales</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US" sz="2000" u="none" baseline="0"/>
               <a:t> / Month</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" sz="2000" u="none"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -6202,8 +5938,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.37216144878928215"/>
-          <c:y val="4.9903629219023152E-2"/>
+          <c:x val="0.38762639152864514"/>
+          <c:y val="4.0230637728216764E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -6219,21 +5955,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:glow rad="101600">
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                    <a:alpha val="60000"/>
-                  </a:schemeClr>
-                </a:glow>
-              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -6281,21 +6009,21 @@
           <a:gradFill rotWithShape="1">
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent4">
                   <a:satMod val="103000"/>
                   <a:lumMod val="102000"/>
                   <a:tint val="94000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="50000">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent4">
                   <a:satMod val="110000"/>
                   <a:lumMod val="100000"/>
                   <a:shade val="100000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="100000">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent4">
                   <a:lumMod val="99000"/>
                   <a:satMod val="120000"/>
                   <a:shade val="78000"/>
@@ -6337,19 +6065,11 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:effectLst>
-                    <a:glow rad="101600">
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                        <a:alpha val="60000"/>
-                      </a:schemeClr>
-                    </a:glow>
-                  </a:effectLst>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
@@ -6410,7 +6130,17 @@
       </c:spPr>
     </c:backWall>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.645777898452349E-2"/>
+          <c:y val="0.17212875764393401"/>
+          <c:w val="0.83057272151325912"/>
+          <c:h val="0.65515775032412882"/>
+        </c:manualLayout>
+      </c:layout>
       <c:bar3DChart>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
@@ -6433,21 +6163,21 @@
             <a:gradFill rotWithShape="1">
               <a:gsLst>
                 <a:gs pos="0">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent4">
                     <a:satMod val="103000"/>
                     <a:lumMod val="102000"/>
                     <a:tint val="94000"/>
                   </a:schemeClr>
                 </a:gs>
                 <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent4">
                     <a:satMod val="110000"/>
                     <a:lumMod val="100000"/>
                     <a:shade val="100000"/>
                   </a:schemeClr>
                 </a:gs>
                 <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent4">
                     <a:lumMod val="99000"/>
                     <a:satMod val="120000"/>
                     <a:shade val="78000"/>
@@ -6602,13 +6332,19 @@
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -6619,19 +6355,11 @@
             <a:pPr>
               <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:glow rad="101600">
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                      <a:alpha val="60000"/>
-                    </a:schemeClr>
-                  </a:glow>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
@@ -6658,9 +6386,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -6669,7 +6397,7 @@
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -6686,19 +6414,11 @@
             <a:pPr>
               <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:glow rad="101600">
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                      <a:alpha val="60000"/>
-                    </a:schemeClr>
-                  </a:glow>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
@@ -6719,45 +6439,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:glow rad="101600">
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                    <a:alpha val="60000"/>
-                  </a:schemeClr>
-                </a:glow>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -6770,57 +6451,26 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
+      <a:round/>
     </a:ln>
-    <a:effectLst>
-      <a:glow rad="101600">
-        <a:schemeClr val="tx1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-          <a:alpha val="60000"/>
-        </a:schemeClr>
-      </a:glow>
-    </a:effectLst>
+    <a:effectLst/>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr>
-          <a:effectLst>
-            <a:glow rad="101600">
-              <a:schemeClr val="tx1">
-                <a:lumMod val="85000"/>
-                <a:lumOff val="15000"/>
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:glow>
-          </a:effectLst>
-        </a:defRPr>
+        <a:defRPr/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -6836,7 +6486,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -8671,42 +8320,8 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="17">
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -8791,33 +8406,35 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="340">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8825,44 +8442,37 @@
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -8881,6 +8491,14 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -8969,18 +8587,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -8990,20 +8611,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9014,17 +8635,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -9033,13 +8654,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9059,14 +8681,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9078,16 +8700,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -9096,17 +8719,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -9115,16 +8738,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -9133,8 +8757,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9160,16 +8785,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9182,14 +8808,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9201,19 +8827,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -9237,8 +8856,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9248,7 +8868,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9256,9 +8876,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9269,8 +8889,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9287,38 +8908,29 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="268">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="261">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea>
@@ -9329,36 +8941,571 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
+      <a:pattFill prst="dkDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="25000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="matte"/>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="78000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="341">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9377,6 +9524,516 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="347">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -9465,18 +10122,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9486,20 +10146,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9513,14 +10173,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -9534,8 +10194,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9547,7 +10208,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -9560,9 +10221,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9577,13 +10238,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -9595,14 +10257,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -9614,13 +10276,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -9629,8 +10292,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9640,7 +10304,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -9648,7 +10312,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -9656,16 +10320,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9678,14 +10343,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9697,19 +10362,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -9718,7 +10376,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -9733,8 +10391,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9744,7 +10403,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9752,9 +10411,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9765,8 +10424,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9776,979 +10436,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="294">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr/>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr/>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -11881,8 +11569,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1070686" y="753154"/>
-          <a:ext cx="1739189" cy="868680"/>
+          <a:off x="1070686" y="758446"/>
+          <a:ext cx="1739189" cy="894080"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -11938,7 +11626,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -12073,8 +11761,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7013436" y="738055"/>
-          <a:ext cx="1885323" cy="882694"/>
+          <a:off x="6990079" y="742143"/>
+          <a:ext cx="1874813" cy="894080"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -12130,7 +11818,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -12138,14 +11826,14 @@
             <a:t>Quantity</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
             <a:t> Sold</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1400" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1" u="sng">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -12194,15 +11882,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>420647</xdr:colOff>
+      <xdr:colOff>446047</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>112011</xdr:rowOff>
+      <xdr:rowOff>95077</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>150444</xdr:colOff>
+      <xdr:colOff>175844</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>89150</xdr:rowOff>
+      <xdr:rowOff>72216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -12231,8 +11919,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7217337" y="1128011"/>
-          <a:ext cx="342900" cy="345001"/>
+          <a:off x="7219380" y="1119544"/>
+          <a:ext cx="339397" cy="349672"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12329,7 +12017,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -12337,14 +12025,14 @@
             <a:t>Total</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
             <a:t> Profit</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1400" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1" u="sng">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -12434,13 +12122,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>51675</xdr:colOff>
+      <xdr:colOff>51674</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>125764</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>554595</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>25399</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>80044</xdr:rowOff>
     </xdr:to>
@@ -12457,8 +12145,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10099189" y="768021"/>
-          <a:ext cx="1722120" cy="890452"/>
+          <a:off x="10101607" y="769231"/>
+          <a:ext cx="1802525" cy="894080"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -12518,7 +12206,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -12526,14 +12214,14 @@
             <a:t>Average</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
             <a:t> Discount</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1400" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1" u="sng">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -12598,15 +12286,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>202174</xdr:colOff>
+      <xdr:colOff>219108</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>107137</xdr:rowOff>
+      <xdr:rowOff>141004</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>518711</xdr:colOff>
+      <xdr:colOff>535645</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>63227</xdr:rowOff>
+      <xdr:rowOff>97094</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -12635,8 +12323,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10249688" y="1130394"/>
-          <a:ext cx="316537" cy="326204"/>
+          <a:off x="10269041" y="1165471"/>
+          <a:ext cx="316537" cy="328623"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12671,8 +12359,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12961060" y="761711"/>
-          <a:ext cx="1722120" cy="890452"/>
+          <a:off x="12963479" y="762921"/>
+          <a:ext cx="1722120" cy="894080"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -12732,7 +12420,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -12740,14 +12428,14 @@
             <a:t>Total</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+            <a:rPr lang="en-US" sz="1600" b="1" u="sng" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
             <a:t> Months</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1400" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1" u="sng">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -12755,7 +12443,7 @@
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-US" sz="600" b="1" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-US" sz="600" b="1" u="sng" strike="noStrike">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -12858,7 +12546,7 @@
       <xdr:col>22</xdr:col>
       <xdr:colOff>609601</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>514350</xdr:rowOff>
+      <xdr:rowOff>973667</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13004,18 +12692,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:colOff>51646</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>117474</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>662940</xdr:colOff>
+      <xdr:colOff>646006</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>556259</xdr:rowOff>
+      <xdr:rowOff>903392</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="33" name="Region">
@@ -13038,7 +12726,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13048,8 +12736,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="68580" y="4119288"/>
-              <a:ext cx="1820567" cy="2252695"/>
+              <a:off x="51646" y="4511674"/>
+              <a:ext cx="1813560" cy="2276051"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -13120,15 +12808,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
+      <xdr:colOff>56727</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>74506</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>746760</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>514350</xdr:rowOff>
+      <xdr:colOff>795867</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>59265</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13158,18 +12846,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:colOff>719666</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2415540</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>160095</xdr:rowOff>
+      <xdr:colOff>2432473</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>347134</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="15" name="Months (Order_Date)">
@@ -13192,7 +12880,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13202,8 +12890,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1988207" y="1859543"/>
-              <a:ext cx="1653540" cy="3196621"/>
+              <a:off x="1938866" y="2472268"/>
+              <a:ext cx="1712807" cy="3759199"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -13397,6 +13085,83 @@
         </a:effectLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>90594</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>761999</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>973666</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Order_Date">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7FF7123-E439-D1CB-3916-6679D8B7D06C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Order_Date"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3815927" y="5638800"/>
+              <a:ext cx="5548205" cy="1219199"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -18192,7 +17957,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{186B8A28-BBE6-4C83-B417-67DA9CF247AC}" name="PivotTable6" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="38">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{186B8A28-BBE6-4C83-B417-67DA9CF247AC}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="45">
   <location ref="A2:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -18471,118 +18236,118 @@
     <dataField name="Sum of Sales" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="62">
-    <format dxfId="7">
+    <format dxfId="134">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="133">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="132">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="131">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="130">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="129">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="128">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="127">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="126">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="125">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="124">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="123">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="122">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="121">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="120">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="119">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="118">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="117">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="116">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="115">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="114">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="113">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="112">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="111">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="110">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="109">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="108">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="107">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="106">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="105">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="104">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="103">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="102">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="101">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="100">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="99">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="98">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="97">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="2">
@@ -18592,10 +18357,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="95">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="9" count="9">
@@ -18615,7 +18380,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="94">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="9" count="4">
@@ -18630,19 +18395,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="93">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="92">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="91">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="90">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="89">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="2">
@@ -18652,10 +18417,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="88">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="87">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="9" count="9">
@@ -18675,7 +18440,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="86">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="9" count="4">
@@ -18690,19 +18455,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="85">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="84">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="83">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="82">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="81">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="2">
@@ -18712,10 +18477,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="80">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="79">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="9" count="9">
@@ -18735,7 +18500,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="78">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="9" count="4">
@@ -18750,19 +18515,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="77">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="76">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="66">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="67">
+    <format dxfId="74">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="68">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -18799,7 +18564,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{40D526B2-B8BF-4DBD-9395-0B9F779928E7}" name="PivotTable37" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{40D526B2-B8BF-4DBD-9395-0B9F779928E7}" name="PivotTable37" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
   <location ref="A12:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -18851,44 +18616,44 @@
     <dataField name="Sum of Quantity" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="80">
+    <format dxfId="18">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="16">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="77">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="76">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="75">
+    <format dxfId="13">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="74">
+    <format dxfId="12">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="73">
+    <format dxfId="11">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="72">
+    <format dxfId="10">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="71">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="69">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -18976,7 +18741,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8C18395-5436-4189-B67F-27A2E7C93725}" name="PivotTable7" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="23" colHeaderCaption="Region">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8C18395-5436-4189-B67F-27A2E7C93725}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="29" colHeaderCaption="Region">
   <location ref="A2:G9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -19248,139 +19013,139 @@
     <dataField name="Total Sales" fld="4" baseField="3" baseItem="0"/>
   </dataFields>
   <formats count="54">
-    <format dxfId="135">
+    <format dxfId="72">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="134">
+    <format dxfId="71">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="133">
+    <format dxfId="70">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="132">
+    <format dxfId="69">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="131">
+    <format dxfId="68">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="130">
+    <format dxfId="67">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="129">
+    <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="128">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="127">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="126">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="125">
+    <format dxfId="62">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="124">
+    <format dxfId="61">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="123">
+    <format dxfId="60">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="122">
+    <format dxfId="59">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="121">
+    <format dxfId="58">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="120">
+    <format dxfId="57">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="119">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="118">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="117">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="116">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="115">
+    <format dxfId="52">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="114">
+    <format dxfId="51">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="113">
+    <format dxfId="50">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="112">
+    <format dxfId="49">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="111">
+    <format dxfId="48">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="110">
+    <format dxfId="47">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="109">
+    <format dxfId="46">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="108">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="107">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="106">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="105">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="104">
+    <format dxfId="41">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="103">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="102">
+    <format dxfId="39">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="101">
+    <format dxfId="38">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="100">
+    <format dxfId="37">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="99">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19389,7 +19154,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="98">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19398,7 +19163,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="97">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19407,7 +19172,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="96">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19416,7 +19181,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="95">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19425,7 +19190,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="94">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19434,7 +19199,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="93">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19443,7 +19208,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="92">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19452,7 +19217,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="91">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -19461,35 +19226,35 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="90">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="89">
+    <format dxfId="26">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="88">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="24">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="23">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="85">
+    <format dxfId="22">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="84">
+    <format dxfId="21">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="83">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -19716,7 +19481,7 @@
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Product_Category" xr10:uid="{A4149174-AF4D-40A6-9B68-AACD1CD83439}" cache="Slicer_Product_Category" caption="Product_Category" startItem="1" style="Slicer Style 1" rowHeight="365760"/>
   <slicer name="Region" xr10:uid="{CAE3929D-77AB-465A-BEC8-C89BF26AB89D}" cache="Slicer_Region" caption="Region" style="Slicer Style 1" rowHeight="365760"/>
-  <slicer name="Months (Order_Date)" xr10:uid="{880F4560-5EDF-4114-A4F3-4103D8145DF8}" cache="Slicer_Months__Order_Date" caption="Months " startItem="4" style="Slicer Style 1" rowHeight="247650"/>
+  <slicer name="Months (Order_Date)" xr10:uid="{880F4560-5EDF-4114-A4F3-4103D8145DF8}" cache="Slicer_Months__Order_Date" caption="Months " startItem="2" style="Slicer Style 1" rowHeight="247650"/>
 </slicers>
 </file>
 
@@ -19765,7 +19530,7 @@
     <tableColumn id="8" xr3:uid="{DB641EB8-FEE4-4C72-8F0B-EC2654FB79B4}" name="Q7. Hight Value Customer" dataDxfId="143">
       <calculatedColumnFormula>IF(RANK(I3, $I$3:$I$29,0)&lt;=10, "YES", "NO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{BDF9B7F0-B307-473C-BF08-56F4EDCC646E}" name="Q6. TimeStamp" dataDxfId="81">
+    <tableColumn id="9" xr3:uid="{BDF9B7F0-B307-473C-BF08-56F4EDCC646E}" name="Q6. TimeStamp" dataDxfId="142">
       <calculatedColumnFormula>NOW()</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -19774,12 +19539,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2C0583E5-9588-4BB5-B677-1D6A405FA230}" name="Statistics" displayName="Statistics" ref="K2:M15" totalsRowShown="0" headerRowDxfId="142" headerRowBorderDxfId="141" tableBorderDxfId="140" totalsRowBorderDxfId="139">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2C0583E5-9588-4BB5-B677-1D6A405FA230}" name="Statistics" displayName="Statistics" ref="K2:M15" totalsRowShown="0" headerRowDxfId="141" headerRowBorderDxfId="140" tableBorderDxfId="139" totalsRowBorderDxfId="138">
   <autoFilter ref="K2:M15" xr:uid="{2C0583E5-9588-4BB5-B677-1D6A405FA230}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C924EFB2-730C-4E5B-B296-B0995E6BEF4B}" name="Statistics" dataDxfId="138"/>
-    <tableColumn id="2" xr3:uid="{C0CDA319-C39C-4D71-B8CD-122017AB6991}" name="Sales" dataDxfId="137"/>
-    <tableColumn id="3" xr3:uid="{6AD1C668-7F04-4A70-BD8E-9BB0041441C9}" name="Profit" dataDxfId="136"/>
+    <tableColumn id="1" xr3:uid="{C924EFB2-730C-4E5B-B296-B0995E6BEF4B}" name="Statistics" dataDxfId="137"/>
+    <tableColumn id="2" xr3:uid="{C0CDA319-C39C-4D71-B8CD-122017AB6991}" name="Sales" dataDxfId="136"/>
+    <tableColumn id="3" xr3:uid="{6AD1C668-7F04-4A70-BD8E-9BB0041441C9}" name="Profit" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -20100,6 +19865,23 @@
 </a:theme>
 </file>
 
+<file path=xl/timelineCaches/timelineCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="NativeTimeline_Order_Date" xr10:uid="{501D30B1-F682-4E0B-ABC3-642EB2245494}" sourceName="Order_Date">
+  <pivotTables>
+    <pivotTable tabId="6" name="PivotTable6"/>
+  </pivotTables>
+  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="769537850" filterType="unknown">
+    <bounds startDate="2024-01-01T00:00:00" endDate="2026-01-01T00:00:00"/>
+  </state>
+</timelineCacheDefinition>
+</file>
+
+<file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <timeline name="Order_Date" xr10:uid="{9FC33B96-8B09-480A-B396-FAEC62D1D3B5}" cache="NativeTimeline_Order_Date" caption="Order_Date" showHeader="0" showHorizontalScrollbar="0" level="2" selectionLevel="2" scrollPosition="2024-12-20T00:00:00"/>
+</timelines>
+</file>
+
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
   <wetp:taskpane dockstate="right" visibility="0" width="438" row="5">
@@ -20336,7 +20118,7 @@
       <c r="L29" s="87"/>
       <c r="W29" s="87"/>
     </row>
-    <row r="30" spans="1:23" ht="47.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" ht="83.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="93"/>
       <c r="B30" s="85"/>
       <c r="C30" s="88"/>
@@ -20361,137 +20143,138 @@
       <c r="V30" s="85"/>
       <c r="W30" s="88"/>
     </row>
-    <row r="31" spans="1:23" ht="14.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="94"/>
-      <c r="B31" s="95"/>
-      <c r="C31" s="86"/>
+    <row r="31" spans="1:23" ht="35.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="124" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="124"/>
+      <c r="C31" s="125"/>
       <c r="L31" s="87"/>
       <c r="W31" s="87"/>
     </row>
-    <row r="32" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="84"/>
-      <c r="C32" s="87"/>
+    <row r="32" spans="1:23" ht="4.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="105"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="106"/>
       <c r="L32" s="87"/>
       <c r="W32" s="87"/>
     </row>
-    <row r="33" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="84"/>
-      <c r="C33" s="87"/>
+    <row r="33" spans="1:23" ht="4.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="105"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="106"/>
       <c r="L33" s="87"/>
       <c r="W33" s="87"/>
     </row>
-    <row r="34" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="98" t="s">
-        <v>159</v>
-      </c>
-      <c r="B34" s="98"/>
-      <c r="C34" s="99"/>
+    <row r="34" spans="1:23" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="105"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="106"/>
       <c r="L34" s="87"/>
       <c r="W34" s="87"/>
     </row>
-    <row r="35" spans="1:23" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="96" t="s">
-        <v>163</v>
-      </c>
-      <c r="B35" s="96"/>
-      <c r="C35" s="97"/>
+    <row r="35" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" s="107"/>
+      <c r="C35" s="108"/>
       <c r="L35" s="87"/>
       <c r="W35" s="87"/>
     </row>
-    <row r="36" spans="1:23" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="96"/>
-      <c r="B36" s="96"/>
-      <c r="C36" s="97"/>
+    <row r="36" spans="1:23" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="107"/>
+      <c r="B36" s="107"/>
+      <c r="C36" s="108"/>
       <c r="L36" s="87"/>
       <c r="W36" s="87"/>
     </row>
     <row r="37" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="96" t="s">
+      <c r="A37" s="107" t="s">
         <v>162</v>
       </c>
-      <c r="B37" s="96"/>
-      <c r="C37" s="97"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="108"/>
       <c r="L37" s="87"/>
       <c r="W37" s="87"/>
     </row>
-    <row r="38" spans="1:23" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="96"/>
-      <c r="B38" s="96"/>
-      <c r="C38" s="97"/>
+    <row r="38" spans="1:23" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="108"/>
       <c r="L38" s="87"/>
       <c r="W38" s="87"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A39" s="96" t="s">
-        <v>161</v>
-      </c>
-      <c r="B39" s="96"/>
-      <c r="C39" s="97"/>
+      <c r="A39" s="107" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" s="107"/>
+      <c r="C39" s="108"/>
       <c r="L39" s="87"/>
       <c r="W39" s="87"/>
     </row>
-    <row r="40" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="96"/>
-      <c r="B40" s="96"/>
-      <c r="C40" s="97"/>
+    <row r="40" spans="1:23" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="107"/>
+      <c r="B40" s="107"/>
+      <c r="C40" s="108"/>
       <c r="L40" s="87"/>
       <c r="W40" s="87"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A41" s="96" t="s">
-        <v>160</v>
-      </c>
-      <c r="B41" s="96"/>
-      <c r="C41" s="97"/>
+      <c r="A41" s="107" t="s">
+        <v>164</v>
+      </c>
+      <c r="B41" s="107"/>
+      <c r="C41" s="108"/>
       <c r="L41" s="87"/>
       <c r="W41" s="87"/>
     </row>
-    <row r="42" spans="1:23" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="96"/>
-      <c r="B42" s="96"/>
-      <c r="C42" s="97"/>
+    <row r="42" spans="1:23" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="107"/>
+      <c r="B42" s="107"/>
+      <c r="C42" s="108"/>
       <c r="L42" s="87"/>
       <c r="W42" s="87"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A43" s="96" t="s">
-        <v>164</v>
-      </c>
-      <c r="B43" s="96"/>
-      <c r="C43" s="97"/>
+      <c r="A43" s="107" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="107"/>
+      <c r="C43" s="108"/>
       <c r="L43" s="87"/>
       <c r="W43" s="87"/>
     </row>
-    <row r="44" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="96"/>
-      <c r="B44" s="96"/>
-      <c r="C44" s="97"/>
+    <row r="44" spans="1:23" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="107"/>
+      <c r="B44" s="107"/>
+      <c r="C44" s="108"/>
       <c r="L44" s="87"/>
       <c r="W44" s="87"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A45" s="96" t="s">
-        <v>165</v>
-      </c>
-      <c r="B45" s="96"/>
-      <c r="C45" s="97"/>
+      <c r="A45" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" s="107"/>
+      <c r="C45" s="108"/>
       <c r="L45" s="87"/>
       <c r="W45" s="87"/>
     </row>
-    <row r="46" spans="1:23" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="96"/>
-      <c r="B46" s="96"/>
-      <c r="C46" s="97"/>
+    <row r="46" spans="1:23" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="107"/>
+      <c r="B46" s="107"/>
+      <c r="C46" s="108"/>
       <c r="L46" s="87"/>
       <c r="W46" s="87"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A47" s="84"/>
+    <row r="47" spans="1:23" ht="6.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="87"/>
       <c r="L47" s="87"/>
       <c r="W47" s="87"/>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="84"/>
       <c r="C48" s="87"/>
       <c r="L48" s="87"/>
@@ -20525,10 +20308,10 @@
     <row r="50" spans="1:23" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A41:C42"/>
     <mergeCell ref="A43:C44"/>
     <mergeCell ref="A45:C46"/>
-    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A35:C36"/>
     <mergeCell ref="A37:C38"/>
     <mergeCell ref="A39:C40"/>
@@ -20541,6 +20324,11 @@
       <x14:slicerList>
         <x14:slicer r:id="rId3"/>
       </x14:slicerList>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
+      <x15:timelineRefs>
+        <x15:timelineRef r:id="rId4"/>
+      </x15:timelineRefs>
     </ext>
   </extLst>
 </worksheet>
@@ -26602,17 +26390,17 @@
       <c r="B1" s="92"/>
       <c r="C1" s="92"/>
       <c r="D1" s="92"/>
-      <c r="E1" s="100" t="s">
+      <c r="E1" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
       <c r="P1" s="18"/>
@@ -26644,8 +26432,8 @@
       <c r="L2" t="s">
         <v>152</v>
       </c>
-      <c r="M2" s="115" t="s">
-        <v>166</v>
+      <c r="M2" s="94" t="s">
+        <v>160</v>
       </c>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
@@ -26681,12 +26469,12 @@
         <v>15</v>
       </c>
       <c r="L3" s="28" t="str">
-        <f>IF(RANK(I3, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" ref="L3:L29" si="0">IF(RANK(I3, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
         <v>NO</v>
       </c>
-      <c r="M3" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M3" s="95">
+        <f t="shared" ref="M3:M29" ca="1" si="1">NOW()</f>
+        <v>46276.457523611112</v>
       </c>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
@@ -26722,12 +26510,12 @@
         <v>5</v>
       </c>
       <c r="L4" s="49" t="str">
-        <f>IF(RANK(I4, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M4" s="119">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M4" s="98">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
@@ -26763,12 +26551,12 @@
         <v>14</v>
       </c>
       <c r="L5" s="28" t="str">
-        <f>IF(RANK(I5, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M5" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M5" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
@@ -26804,12 +26592,12 @@
         <v>13</v>
       </c>
       <c r="L6" s="28" t="str">
-        <f>IF(RANK(I6, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M6" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M6" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
@@ -26845,12 +26633,12 @@
         <v>9</v>
       </c>
       <c r="L7" s="28" t="str">
-        <f>IF(RANK(I7, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M7" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M7" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
@@ -26886,12 +26674,12 @@
         <v>8</v>
       </c>
       <c r="L8" s="49" t="str">
-        <f>IF(RANK(I8, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M8" s="119">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M8" s="98">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
@@ -26927,12 +26715,12 @@
         <v>6</v>
       </c>
       <c r="L9" s="28" t="str">
-        <f>IF(RANK(I9, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M9" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M9" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
@@ -26968,12 +26756,12 @@
         <v>9</v>
       </c>
       <c r="L10" s="49" t="str">
-        <f>IF(RANK(I10, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M10" s="119">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M10" s="98">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -27009,12 +26797,12 @@
         <v>9</v>
       </c>
       <c r="L11" s="28" t="str">
-        <f>IF(RANK(I11, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M11" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M11" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N11" s="16"/>
       <c r="O11" s="16"/>
@@ -27050,12 +26838,12 @@
         <v>8</v>
       </c>
       <c r="L12" s="28" t="str">
-        <f>IF(RANK(I12, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M12" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M12" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="16"/>
@@ -27091,12 +26879,12 @@
         <v>13</v>
       </c>
       <c r="L13" s="49" t="str">
-        <f>IF(RANK(I13, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M13" s="119">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M13" s="98">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N13" s="16"/>
       <c r="O13" s="16"/>
@@ -27132,12 +26920,12 @@
         <v>5</v>
       </c>
       <c r="L14" s="28" t="str">
-        <f>IF(RANK(I14, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M14" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M14" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
@@ -27173,12 +26961,12 @@
         <v>3</v>
       </c>
       <c r="L15" s="28" t="str">
-        <f>IF(RANK(I15, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M15" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M15" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
@@ -27214,12 +27002,12 @@
         <v>0</v>
       </c>
       <c r="L16" s="28" t="str">
-        <f>IF(RANK(I16, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M16" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M16" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
@@ -27255,12 +27043,12 @@
         <v>6</v>
       </c>
       <c r="L17" s="28" t="str">
-        <f>IF(RANK(I17, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M17" s="116">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M17" s="95">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
@@ -27296,12 +27084,12 @@
         <v>8</v>
       </c>
       <c r="L18" s="28" t="str">
-        <f>IF(RANK(I18, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M18" s="117">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M18" s="96">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
@@ -27337,12 +27125,12 @@
         <v>11</v>
       </c>
       <c r="L19" s="28" t="str">
-        <f>IF(RANK(I19, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M19" s="118">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M19" s="97">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -27373,12 +27161,12 @@
         <v>7</v>
       </c>
       <c r="L20" s="49" t="str">
-        <f>IF(RANK(I20, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M20" s="120">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M20" s="99">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -27409,12 +27197,12 @@
         <v>9</v>
       </c>
       <c r="L21" s="49" t="str">
-        <f>IF(RANK(I21, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M21" s="120">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M21" s="99">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -27445,12 +27233,12 @@
         <v>8</v>
       </c>
       <c r="L22" s="49" t="str">
-        <f>IF(RANK(I22, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M22" s="120">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M22" s="99">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -27481,12 +27269,12 @@
         <v>9</v>
       </c>
       <c r="L23" s="49" t="str">
-        <f>IF(RANK(I23, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M23" s="120">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M23" s="99">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -27517,12 +27305,12 @@
         <v>13</v>
       </c>
       <c r="L24" s="28" t="str">
-        <f>IF(RANK(I24, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M24" s="118">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M24" s="97">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -27553,12 +27341,12 @@
         <v>8</v>
       </c>
       <c r="L25" s="28" t="str">
-        <f>IF(RANK(I25, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M25" s="118">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M25" s="97">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -27589,12 +27377,12 @@
         <v>15</v>
       </c>
       <c r="L26" s="49" t="str">
-        <f>IF(RANK(I26, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M26" s="120">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M26" s="99">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -27625,12 +27413,12 @@
         <v>12</v>
       </c>
       <c r="L27" s="49" t="str">
-        <f>IF(RANK(I27, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M27" s="120">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M27" s="99">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -27661,12 +27449,12 @@
         <v>14</v>
       </c>
       <c r="L28" s="28" t="str">
-        <f>IF(RANK(I28, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M28" s="118">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M28" s="97">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -27697,12 +27485,12 @@
         <v>12</v>
       </c>
       <c r="L29" s="28" t="str">
-        <f>IF(RANK(I29, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
+        <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M29" s="118">
-        <f ca="1">NOW()</f>
-        <v>46275.69037546296</v>
+      <c r="M29" s="97">
+        <f t="shared" ca="1" si="1"/>
+        <v>46276.457523611112</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -27762,22 +27550,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="110" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
     </row>
     <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="111" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="102"/>
+      <c r="B3" s="111"/>
       <c r="D3" s="74" t="s">
         <v>148</v>
       </c>
@@ -27865,10 +27653,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="111" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="102"/>
+      <c r="B8" s="111"/>
       <c r="D8" s="58">
         <v>0.2</v>
       </c>
@@ -27975,28 +27763,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="110" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="K1" s="105" t="s">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="K1" s="114" t="s">
         <v>156</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="107"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="116"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="112" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="104"/>
+      <c r="B2" s="113"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -28484,21 +28272,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="110"/>
-      <c r="E1" s="111" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="119"/>
+      <c r="E1" s="120" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="75" t="s">
@@ -28902,25 +28690,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="117" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="110"/>
-      <c r="I1" s="112" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="119"/>
+      <c r="I1" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="114"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="123"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
@@ -29097,58 +28885,58 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="121" t="s">
+      <c r="A12" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="B12" s="121" t="s">
+      <c r="B12" s="100" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="122" t="s">
+      <c r="A13" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="123">
+      <c r="B13" s="102">
         <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="122" t="s">
+      <c r="A14" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="123">
+      <c r="B14" s="102">
         <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="122" t="s">
+      <c r="A15" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="123">
+      <c r="B15" s="102">
         <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="122" t="s">
+      <c r="A16" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="123">
+      <c r="B16" s="102">
         <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="122" t="s">
+      <c r="A17" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="123">
+      <c r="B17" s="102">
         <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="124" t="s">
+      <c r="A18" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="125">
+      <c r="B18" s="104">
         <v>1999</v>
       </c>
     </row>
@@ -29160,13 +28948,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{812DE360-3A6B-48DA-BB18-FAC9807D0CB5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>